--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios166.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios166.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.10364683466651</v>
+        <v>36.61501104665028</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.62585088809356</v>
+        <v>24.36595408175734</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.44179664332285</v>
+        <v>26.70813236786437</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.04520712300119</v>
+        <v>23.11942269427218</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.51250499876946</v>
+        <v>24.01057510522273</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.33858961946316</v>
+        <v>26.55079382853593</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32.3623464325932</v>
+        <v>35.96488557229039</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.35367971377437</v>
+        <v>23.83911930384651</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.0051314415204</v>
+        <v>26.81908269406452</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.53439828100605</v>
+        <v>22.5675251326053</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.22569088535312</v>
+        <v>23.88147140762687</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.19143591942859</v>
+        <v>26.36718737657444</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.8781604193181</v>
+        <v>36.60696079697056</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31.30896580576047</v>
+        <v>24.01523149180507</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.6604250551914</v>
+        <v>26.78022345953322</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31.11853714406958</v>
+        <v>23.2708467030666</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30.90190026810807</v>
+        <v>23.77874494216852</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26.38537473627143</v>
+        <v>26.22981420610331</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.98219331339706</v>
+        <v>36.64272146309074</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32.04219171981372</v>
+        <v>23.59691872119686</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25.67314352054306</v>
+        <v>26.74553807290743</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30.93076622530664</v>
+        <v>23.25366536523942</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>30.87763749399261</v>
+        <v>24.25294211100709</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.56427213857048</v>
+        <v>26.15180188357588</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.76706166132012</v>
+        <v>36.45061435089863</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.145550423716</v>
+        <v>24.18769286211076</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25.36471710217737</v>
+        <v>26.92916997358945</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.97437805757067</v>
+        <v>23.07399702543739</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30.65494821779851</v>
+        <v>24.078316428464</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.17776330947961</v>
+        <v>26.68275571067927</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>32.40773925795113</v>
+        <v>36.63981437568884</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31.73503002992478</v>
+        <v>24.12927391139931</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>24.84927728686636</v>
+        <v>27.14425550195719</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>31.03589880459271</v>
+        <v>22.99298009998337</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30.64313884021754</v>
+        <v>23.70458456153255</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26.48829126400832</v>
+        <v>26.20493698360962</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31.87699555357126</v>
+        <v>29.22884979110496</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27.949041351114</v>
+        <v>31.64481838500263</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>33.76481315925036</v>
+        <v>27.31132552002312</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>23.86187172577242</v>
+        <v>27.65528267089861</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.81346649226352</v>
+        <v>26.95134873357801</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25.59227028038825</v>
+        <v>31.16993281400231</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>31.54268011393102</v>
+        <v>29.59613621477876</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.47591747801738</v>
+        <v>31.57901103504418</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>33.65172476214673</v>
+        <v>27.70091758353298</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>23.82402980161193</v>
+        <v>27.39491654571779</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.02581326446288</v>
+        <v>26.939543593919</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25.25041616300936</v>
+        <v>31.97399879228457</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31.25512922946111</v>
+        <v>29.95386284614248</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>28.48319327701522</v>
+        <v>31.53571869302465</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>33.78787675956675</v>
+        <v>27.67524082865436</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>24.00221668533945</v>
+        <v>27.49183439977261</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.34614302831867</v>
+        <v>26.73208506885241</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25.18277917517818</v>
+        <v>32.15423606169546</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31.57574635170642</v>
+        <v>29.77369967585042</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>28.3712666883873</v>
+        <v>31.75631984132824</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>33.6145178583084</v>
+        <v>27.50809173271227</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.16641288192525</v>
+        <v>27.74520122414244</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28.21270357101349</v>
+        <v>27.39386631439327</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25.38338363825001</v>
+        <v>32.36210518362653</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>31.79682770414062</v>
+        <v>29.79733721533292</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>28.01520144165015</v>
+        <v>31.5523214087633</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>34.03824861076384</v>
+        <v>27.19770120378824</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>23.89700963537663</v>
+        <v>27.62346137097919</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28.49129830576527</v>
+        <v>27.22086310782818</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>24.89933126538056</v>
+        <v>32.07194573110122</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>31.05026839579908</v>
+        <v>29.90514081460254</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>28.37602263333863</v>
+        <v>31.50219412717263</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>34.37836937222971</v>
+        <v>28.13722761830613</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>23.75418277475058</v>
+        <v>27.09530930338309</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.38505028624036</v>
+        <v>27.26505561521039</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25.58174909299745</v>
+        <v>31.59184908766303</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30.48428036067273</v>
+        <v>31.08919999323964</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30.91055131731069</v>
+        <v>24.46082200282565</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>25.67531822995366</v>
+        <v>25.76703616980916</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>23.93787887416009</v>
+        <v>28.35749532345462</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.75625591015565</v>
+        <v>28.97310926107909</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>29.66749338153724</v>
+        <v>29.3347081835513</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30.20538540738085</v>
+        <v>31.21585957686649</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>31.10638390331014</v>
+        <v>24.73293989299708</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>26.00905251202691</v>
+        <v>26.17370467357696</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>24.33503053984881</v>
+        <v>28.69557383574636</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32.56267602759701</v>
+        <v>28.83799076884545</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>28.68191575780155</v>
+        <v>28.62372985045924</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30.56443984279313</v>
+        <v>31.30779841172264</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>31.75963992658631</v>
+        <v>24.19365187113187</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25.63904092948433</v>
+        <v>26.27299766443968</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>24.10936685926676</v>
+        <v>28.82284152406084</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.85192766263893</v>
+        <v>28.79941189901623</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>29.28642945070055</v>
+        <v>29.19273040923187</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>30.25429576524007</v>
+        <v>31.21083393612077</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>31.43731426246646</v>
+        <v>24.55447470080126</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26.22276897632837</v>
+        <v>26.32287468431801</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>23.72710357269199</v>
+        <v>27.99203035424526</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>32.67020075106026</v>
+        <v>28.90398818148627</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>28.54779403396402</v>
+        <v>29.21790600988731</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>30.5969492128901</v>
+        <v>30.76384906673127</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>31.46887525702278</v>
+        <v>24.83760071310635</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>26.23347011612592</v>
+        <v>26.24053883027346</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>24.13578330297961</v>
+        <v>28.60692088371246</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32.12965821907887</v>
+        <v>28.84350298426472</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>29.35668827089174</v>
+        <v>28.51045136625156</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30.74404319786309</v>
+        <v>31.86293275710845</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.8286533053222</v>
+        <v>24.49003434438781</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>25.70755742732609</v>
+        <v>26.15645610810832</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>23.94425929349594</v>
+        <v>28.71226302610067</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>32.57484558813435</v>
+        <v>29.18375588740474</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>28.74065486307027</v>
+        <v>29.5675720364053</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>23.7640877562682</v>
+        <v>31.46035483174127</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>28.02974446476371</v>
+        <v>27.27678721390343</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>19.26322593379006</v>
+        <v>24.85768546060265</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>26.22768106459099</v>
+        <v>32.33091517941675</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>27.19655558824145</v>
+        <v>33.13170254688389</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>29.13428663729668</v>
+        <v>25.89663664246797</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>23.28246866623838</v>
+        <v>31.41470793911821</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>28.21523545922311</v>
+        <v>27.9087270594772</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>20.02012765018553</v>
+        <v>24.84478685902134</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>26.21296412776814</v>
+        <v>32.49684236159603</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>27.19896985803316</v>
+        <v>32.96025191148829</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>29.1440799930109</v>
+        <v>26.53342676974045</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>23.37319004573725</v>
+        <v>31.15766390852504</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.76475348599133</v>
+        <v>27.24542326850315</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>19.91306574119354</v>
+        <v>24.90965857704992</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>26.25922728388252</v>
+        <v>31.70375296423111</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>27.71198386796264</v>
+        <v>32.71004575924231</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>29.52214376620295</v>
+        <v>26.3486670834847</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>23.20837719120959</v>
+        <v>31.97261630387625</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>28.21894459589361</v>
+        <v>27.5772532015928</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>19.61017286012821</v>
+        <v>25.06032065330259</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>26.3208864582867</v>
+        <v>32.5720109585573</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>27.15058107679666</v>
+        <v>32.48212329691618</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>28.85779125933553</v>
+        <v>26.23881815603941</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>23.43405259144363</v>
+        <v>32.17389733760918</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>27.24075451334288</v>
+        <v>27.44490783012684</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>19.45178089171057</v>
+        <v>25.18265266463907</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>26.09258236444718</v>
+        <v>32.50737918638745</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>27.31407287421587</v>
+        <v>32.31371730396696</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>29.04845325382222</v>
+        <v>26.36380632232441</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>22.9995175807261</v>
+        <v>31.45812245548168</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.76042582828006</v>
+        <v>27.55726863870246</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>19.87590023111266</v>
+        <v>24.71680116977783</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>26.29104872978423</v>
+        <v>31.8374681854077</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>27.28714567509448</v>
+        <v>32.64239245784527</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>29.49342031110172</v>
+        <v>26.25650283852013</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>29.45539905284304</v>
+        <v>24.56295224264914</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>24.21796343811622</v>
+        <v>29.48955167040217</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29.34969916956648</v>
+        <v>29.12366368587686</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>23.64886142364135</v>
+        <v>20.46184813401272</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.95682872913493</v>
+        <v>30.44671738743053</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>23.07919934175498</v>
+        <v>24.2752332126218</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>29.53986344390422</v>
+        <v>24.32625395262585</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>24.7424403131139</v>
+        <v>28.78002571229554</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>29.34311129138967</v>
+        <v>28.88831355398975</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>24.30821035516545</v>
+        <v>20.43350690288764</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.93043573175123</v>
+        <v>30.92054761618962</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>23.1612529588698</v>
+        <v>24.62477679905246</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>29.33239499604041</v>
+        <v>24.05570161197061</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>24.5729120944391</v>
+        <v>29.23337734365433</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>29.8664161214055</v>
+        <v>28.52271857128686</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>23.93894941148801</v>
+        <v>20.09644856985433</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>31.05802086417034</v>
+        <v>30.91926389912475</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>23.11954608572085</v>
+        <v>24.67126923162569</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>29.2997859628582</v>
+        <v>24.39376049420418</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>24.07804292125942</v>
+        <v>28.96922580872931</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>30.0629926048433</v>
+        <v>28.81160952501101</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>23.87266907168159</v>
+        <v>20.31501683244106</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>31.03954041354615</v>
+        <v>30.40931529718217</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>23.08922105507471</v>
+        <v>24.0720138182351</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>29.16028265000337</v>
+        <v>24.25615857284574</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>24.15442194791822</v>
+        <v>28.98632939294933</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>29.50693786947364</v>
+        <v>28.72578045844682</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>23.55526815628308</v>
+        <v>20.4245024698083</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30.90111829536242</v>
+        <v>30.689337170056</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>22.88128934308641</v>
+        <v>24.51212687115243</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>29.25960683773344</v>
+        <v>24.2401949241227</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>24.02373783978582</v>
+        <v>29.49130340597395</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>29.90145981271461</v>
+        <v>28.74570853393055</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>24.01017767507853</v>
+        <v>20.76220978204494</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>31.4338602982514</v>
+        <v>30.86387165123882</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>22.76600418371595</v>
+        <v>24.32281765216876</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>27.69366519217881</v>
+        <v>28.10444343563301</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>29.49112947397133</v>
+        <v>25.09198352058022</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>27.97315964286023</v>
+        <v>25.17001669749823</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>31.36965053964902</v>
+        <v>31.61700331870587</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>30.19054732283177</v>
+        <v>28.77396309774468</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>27.0259309929793</v>
+        <v>29.60911987939368</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>27.42537456310824</v>
+        <v>28.41253420731587</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>29.80259773772288</v>
+        <v>25.78571647678767</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>27.89227950222648</v>
+        <v>25.39973907403622</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>31.55056874711964</v>
+        <v>32.56077700995358</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>29.22797891468827</v>
+        <v>28.32380761714712</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>27.66861015988876</v>
+        <v>29.72091457650063</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>27.57926156184489</v>
+        <v>28.20657601723487</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>29.42914923127908</v>
+        <v>25.69776167077741</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>28.28949346762425</v>
+        <v>24.85266055569249</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>31.87738117711972</v>
+        <v>31.43725761121011</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>29.73548981102386</v>
+        <v>28.63003804063001</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>26.73238764054315</v>
+        <v>30.22751588973308</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>27.71330309494126</v>
+        <v>28.42357025356041</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>29.46719385123389</v>
+        <v>25.11523836073786</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>27.8129790117513</v>
+        <v>25.1177173367731</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>31.80806684340368</v>
+        <v>32.43121958215946</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>29.95607964610214</v>
+        <v>28.48278227316692</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>27.45691254962342</v>
+        <v>29.48505688298191</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>27.59694763191231</v>
+        <v>28.77849839265977</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>30.05803471168254</v>
+        <v>25.71675188922762</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>28.24880514999356</v>
+        <v>25.74595399689092</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>31.74296927335695</v>
+        <v>31.59453607859151</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>30.07741132346207</v>
+        <v>28.22369695730966</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>27.83843475514362</v>
+        <v>29.80537486612851</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>27.53756473345985</v>
+        <v>28.45456275903036</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29.34570394049534</v>
+        <v>25.55215852080336</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>27.36689138613504</v>
+        <v>25.79784660058011</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>31.8046677710496</v>
+        <v>31.34454673094356</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>29.86195552271608</v>
+        <v>28.90720002153263</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>27.18450816624307</v>
+        <v>29.43931835410009</v>
       </c>
     </row>
   </sheetData>
